--- a/ADP01DX.xlsx
+++ b/ADP01DX.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
   <si>
     <t/>
   </si>
@@ -239,21 +239,6 @@
   </si>
   <si>
     <t>IDM DIAPER ADULT 7L</t>
-  </si>
-  <si>
-    <t>20090847</t>
-  </si>
-  <si>
-    <t>CERTAINTY POPOK 8S/M</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>20090848</t>
-  </si>
-  <si>
-    <t>CERTAINTY POPOK 7S/L</t>
   </si>
 </sst>
 </file>
@@ -646,13 +631,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1276,46 +1260,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
